--- a/HDR_files/Area country list- with extra sheets.xlsx
+++ b/HDR_files/Area country list- with extra sheets.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Me\Documents\UC_MASTER APPLIED DATA SCIENCE\DATA601\PROJECT\myWVSapp\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Me\Documents\UC_MASTER APPLIED DATA SCIENCE\DATA601\PROJECT\GitHub_WVsa_Original version\WorldView\HDR_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9710D4D5-773A-4235-A775-A81FC023FD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6EFBEF-C83D-4186-B377-4DE2B313FA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" tabRatio="717" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" tabRatio="809" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hdi_groups" sheetId="2" r:id="rId1"/>
     <sheet name="regions" sheetId="4" r:id="rId2"/>
     <sheet name="special_groups" sheetId="7" r:id="rId3"/>
-    <sheet name="sources(links)" sheetId="8" r:id="rId4"/>
-    <sheet name="wide table" sheetId="1" r:id="rId5"/>
-    <sheet name="LDCs" sheetId="3" r:id="rId6"/>
-    <sheet name="OECD" sheetId="5" r:id="rId7"/>
-    <sheet name="SIDS" sheetId="6" r:id="rId8"/>
+    <sheet name="DCs" sheetId="9" r:id="rId4"/>
+    <sheet name="sources(links)" sheetId="8" r:id="rId5"/>
+    <sheet name="wide table" sheetId="1" r:id="rId6"/>
+    <sheet name="LDCs" sheetId="3" r:id="rId7"/>
+    <sheet name="OECD" sheetId="5" r:id="rId8"/>
+    <sheet name="SIDS" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="253">
   <si>
     <t>https://www.un.org/ohrlls/content/least-developed-countries</t>
   </si>
@@ -714,9 +715,6 @@
     <t>country</t>
   </si>
   <si>
-    <t>https://hdr.undp.org/data-center/documentation-and-downloads</t>
-  </si>
-  <si>
     <t>https://www.oecd.org/en/about.html</t>
   </si>
   <si>
@@ -771,15 +769,6 @@
     <t>area</t>
   </si>
   <si>
-    <t>Sources for specials groups:</t>
-  </si>
-  <si>
-    <t>Source for Developing regions</t>
-  </si>
-  <si>
-    <t>Sources LCDs:</t>
-  </si>
-  <si>
     <t>https://www.oecd.org/en/about/members-partners.html</t>
   </si>
   <si>
@@ -787,6 +776,33 @@
   </si>
   <si>
     <t>On OECD webiste list of partner it written "Korea" but the official HDR / UN naming list of countries it is Korea (Republic of):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebanon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syrian Arab Republic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Arab Emirates </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myanmar </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tonga</t>
+  </si>
+  <si>
+    <t>Republic of Moldov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamaica </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sierra Leone</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> United Republic of Tanzania</t>
   </si>
 </sst>
 </file>
@@ -892,7 +908,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -900,7 +916,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1205,7 +1220,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>222</v>
@@ -2770,7 +2785,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>222</v>
@@ -3996,7 +4011,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>222</v>
@@ -4005,7 +4020,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -4014,7 +4029,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -4022,7 +4037,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -4031,7 +4046,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -4039,7 +4054,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -4047,7 +4062,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -4055,7 +4070,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -4063,7 +4078,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -4071,7 +4086,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -4079,7 +4094,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -4087,7 +4102,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -4095,7 +4110,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -4103,7 +4118,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -4111,7 +4126,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
@@ -4119,7 +4134,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
@@ -4127,7 +4142,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
@@ -4135,7 +4150,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
@@ -4143,7 +4158,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
@@ -4151,7 +4166,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
@@ -4159,7 +4174,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
@@ -4167,7 +4182,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
@@ -4175,7 +4190,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
@@ -4183,7 +4198,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -4191,7 +4206,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
@@ -4199,7 +4214,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
@@ -4207,7 +4222,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
@@ -4215,7 +4230,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s">
         <v>28</v>
@@ -4223,7 +4238,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
@@ -4231,7 +4246,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B30" t="s">
         <v>30</v>
@@ -4239,7 +4254,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -4247,7 +4262,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B32" t="s">
         <v>32</v>
@@ -4255,7 +4270,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
@@ -4263,7 +4278,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
@@ -4271,7 +4286,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B35" t="s">
         <v>35</v>
@@ -4279,7 +4294,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s">
         <v>36</v>
@@ -4287,7 +4302,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B37" t="s">
         <v>37</v>
@@ -4295,7 +4310,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s">
         <v>38</v>
@@ -4303,7 +4318,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s">
         <v>39</v>
@@ -4311,7 +4326,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s">
         <v>40</v>
@@ -4319,7 +4334,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s">
         <v>41</v>
@@ -4327,7 +4342,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s">
         <v>42</v>
@@ -4335,7 +4350,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -4343,7 +4358,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B44" t="s">
         <v>44</v>
@@ -4351,7 +4366,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s">
         <v>45</v>
@@ -4359,311 +4374,311 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B46" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B46" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>239</v>
-      </c>
-      <c r="B47" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B47" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>239</v>
-      </c>
-      <c r="B48" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B48" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>239</v>
-      </c>
-      <c r="B49" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B49" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>239</v>
-      </c>
-      <c r="B50" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>239</v>
-      </c>
-      <c r="B51" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B51" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>239</v>
-      </c>
-      <c r="B52" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B52" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>239</v>
-      </c>
-      <c r="B53" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B53" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>239</v>
-      </c>
-      <c r="B54" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B54" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>239</v>
-      </c>
-      <c r="B55" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B55" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>239</v>
-      </c>
-      <c r="B56" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B56" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>239</v>
-      </c>
-      <c r="B57" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B57" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>239</v>
-      </c>
-      <c r="B58" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B58" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>239</v>
-      </c>
-      <c r="B59" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B59" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>239</v>
-      </c>
-      <c r="B60" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B60" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>239</v>
-      </c>
-      <c r="B61" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B61" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>239</v>
-      </c>
-      <c r="B62" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B62" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>239</v>
-      </c>
-      <c r="B63" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B63" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>239</v>
-      </c>
-      <c r="B64" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B64" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>239</v>
-      </c>
-      <c r="B65" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>239</v>
-      </c>
-      <c r="B66" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>239</v>
-      </c>
-      <c r="B67" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B67" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>239</v>
-      </c>
-      <c r="B68" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B68" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>239</v>
-      </c>
-      <c r="B69" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B69" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>239</v>
-      </c>
-      <c r="B70" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B70" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>239</v>
-      </c>
-      <c r="B71" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B71" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>239</v>
-      </c>
-      <c r="B72" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B72" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>239</v>
-      </c>
-      <c r="B73" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B73" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>239</v>
-      </c>
-      <c r="B74" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B74" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>239</v>
-      </c>
-      <c r="B75" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B75" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>239</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>225</v>
+        <v>238</v>
+      </c>
+      <c r="B76" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>239</v>
-      </c>
-      <c r="B77" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B77" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>239</v>
-      </c>
-      <c r="B78" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B78" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>239</v>
-      </c>
-      <c r="B79" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B79" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>239</v>
-      </c>
-      <c r="B80" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B80" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>239</v>
-      </c>
-      <c r="B81" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B81" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>239</v>
-      </c>
-      <c r="B82" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B82" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>239</v>
-      </c>
-      <c r="B83" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B83" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>104</v>
@@ -4672,7 +4687,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B85" t="s">
         <v>106</v>
@@ -4680,7 +4695,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B86" t="s">
         <v>107</v>
@@ -4688,7 +4703,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B87" t="s">
         <v>108</v>
@@ -4696,7 +4711,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B88" t="s">
         <v>146</v>
@@ -4704,7 +4719,7 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B89" t="s">
         <v>11</v>
@@ -4712,15 +4727,15 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B91" t="s">
         <v>114</v>
@@ -4728,7 +4743,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B92" t="s">
         <v>115</v>
@@ -4736,7 +4751,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B93" t="s">
         <v>116</v>
@@ -4744,7 +4759,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B94" t="s">
         <v>67</v>
@@ -4752,7 +4767,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B95" t="s">
         <v>119</v>
@@ -4760,7 +4775,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B96" t="s">
         <v>18</v>
@@ -4768,7 +4783,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B97" t="s">
         <v>121</v>
@@ -4776,7 +4791,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B98" t="s">
         <v>19</v>
@@ -4784,7 +4799,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B99" t="s">
         <v>123</v>
@@ -4792,7 +4807,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B100" t="s">
         <v>20</v>
@@ -4800,7 +4815,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B101" t="s">
         <v>140</v>
@@ -4808,7 +4823,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B102" t="s">
         <v>72</v>
@@ -4816,7 +4831,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B103" t="s">
         <v>216</v>
@@ -4824,7 +4839,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B104" t="s">
         <v>155</v>
@@ -4832,7 +4847,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B105" t="s">
         <v>75</v>
@@ -4840,15 +4855,15 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B106" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B107" t="s">
         <v>76</v>
@@ -4856,7 +4871,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B108" t="s">
         <v>77</v>
@@ -4864,7 +4879,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B109" t="s">
         <v>79</v>
@@ -4872,15 +4887,15 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B110" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B111" t="s">
         <v>80</v>
@@ -4888,7 +4903,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B112" t="s">
         <v>35</v>
@@ -4896,31 +4911,31 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B113" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B115" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B116" t="s">
         <v>132</v>
@@ -4928,7 +4943,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B117" t="s">
         <v>39</v>
@@ -4936,7 +4951,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B118" t="s">
         <v>82</v>
@@ -4944,7 +4959,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B119" t="s">
         <v>133</v>
@@ -4952,7 +4967,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B120" t="s">
         <v>41</v>
@@ -4960,7 +4975,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B121" t="s">
         <v>83</v>
@@ -4968,7 +4983,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B122" t="s">
         <v>159</v>
@@ -4980,63 +4995,1544 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908039DF-DC2A-4619-A6B7-9A3A18EBFC54}">
-  <dimension ref="B2:B16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B7753F-7FB8-4E16-A423-B76D157661F1}">
+  <dimension ref="A1:A151"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="2" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="1" t="s">
-        <v>1</v>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{55F4D230-3C55-4C7A-AAB4-2BD500EC0FA5}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{0F02585D-7EB4-4D64-BD12-3AAE99C268BB}"/>
-    <hyperlink ref="B9" r:id="rId3" xr:uid="{2616C037-6C1A-47BF-BEC8-43D12B1CEE54}"/>
-    <hyperlink ref="B16" r:id="rId4" xr:uid="{EB8A641F-9B69-4B60-B913-03F1E4C646A7}"/>
-    <hyperlink ref="B14" r:id="rId5" xr:uid="{14B352CD-AE02-426A-BCCC-4C6AC6772B40}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908039DF-DC2A-4619-A6B7-9A3A18EBFC54}">
+  <dimension ref="A1:B151"/>
+  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y75"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
@@ -6875,7 +8371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0B71AB-5287-47DA-8587-53D9CE1BB25C}">
   <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
@@ -7123,17 +8619,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0252846-CD97-4BE1-B29F-E380B600BDAD}">
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
-  <cols>
-    <col min="2" max="2" width="8.7265625" style="7"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>222</v>
@@ -7141,335 +8634,335 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B2" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B4" t="s">
         <v>172</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" t="s">
         <v>111</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>226</v>
-      </c>
-      <c r="B8" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B8" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>226</v>
-      </c>
-      <c r="B9" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
+      <c r="H10" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B11" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B11" t="s">
         <v>196</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
+      <c r="H11" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" t="s">
         <v>174</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B13" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B13" t="s">
         <v>186</v>
       </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>226</v>
-      </c>
-      <c r="B14" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B14" t="s">
         <v>167</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>226</v>
-      </c>
-      <c r="B15" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" t="s">
         <v>194</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="12"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="11"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>226</v>
-      </c>
-      <c r="B16" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>226</v>
-      </c>
-      <c r="B18" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B18" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>226</v>
-      </c>
-      <c r="B19" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B20" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B20" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>226</v>
-      </c>
-      <c r="B21" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B21" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>226</v>
-      </c>
-      <c r="B22" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>226</v>
-      </c>
-      <c r="B23" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>226</v>
-      </c>
-      <c r="B24" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>226</v>
-      </c>
-      <c r="B25" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>226</v>
-      </c>
-      <c r="B26" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B26" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>226</v>
-      </c>
-      <c r="B27" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B27" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>226</v>
-      </c>
-      <c r="B28" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B28" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>226</v>
-      </c>
-      <c r="B29" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>226</v>
-      </c>
-      <c r="B30" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B30" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>226</v>
-      </c>
-      <c r="B31" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>226</v>
-      </c>
-      <c r="B32" s="7" t="s">
         <v>225</v>
+      </c>
+      <c r="B32" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>226</v>
-      </c>
-      <c r="B33" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B33" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>226</v>
-      </c>
-      <c r="B34" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B34" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>226</v>
-      </c>
-      <c r="B35" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B35" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>226</v>
-      </c>
-      <c r="B36" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>226</v>
-      </c>
-      <c r="B37" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>226</v>
-      </c>
-      <c r="B38" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B38" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>226</v>
-      </c>
-      <c r="B39" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B39" t="s">
         <v>179</v>
       </c>
     </row>
@@ -7482,17 +8975,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACEA95B-5970-4F3F-B45D-032EFB8C37CE}">
   <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" t="s">
         <v>236</v>
-      </c>
-      <c r="F1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7500,7 +8993,7 @@
         <v>104</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7513,7 +9006,7 @@
         <v>107</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7533,7 +9026,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7613,7 +9106,7 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -7633,7 +9126,7 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -7648,17 +9141,17 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:1">
